--- a/Data/Drugcode_a_verifier.xlsx
+++ b/Data/Drugcode_a_verifier.xlsx
@@ -1,23 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FrédérickProvost\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mantrapharma.sharepoint.com/sites/602/Documents partages/602-2 Courrier, courriel et messagerie/POWER BI/PowerBI/Affaires Règlementaires/Archives/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{22615A91-E262-420B-84D6-BBEA28052701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{22615A91-E262-420B-84D6-BBEA28052701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76CFC39A-0FAA-4C2D-B20C-B8C94F12E8B8}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4E4CF4C5-DE0A-4A25-92E1-A8C1694B9CC3}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
   <si>
     <t>Drug_code</t>
   </si>
@@ -134,24 +131,12 @@
     <t>94057</t>
   </si>
   <si>
-    <t>99162</t>
-  </si>
-  <si>
     <t>93170</t>
   </si>
   <si>
     <t>103590</t>
   </si>
   <si>
-    <t>90466</t>
-  </si>
-  <si>
-    <t>90467</t>
-  </si>
-  <si>
-    <t>91167</t>
-  </si>
-  <si>
     <t>97082</t>
   </si>
   <si>
@@ -161,15 +146,6 @@
     <t>97084</t>
   </si>
   <si>
-    <t>85700</t>
-  </si>
-  <si>
-    <t>85701</t>
-  </si>
-  <si>
-    <t>85702</t>
-  </si>
-  <si>
     <t>90695</t>
   </si>
   <si>
@@ -203,12 +179,6 @@
     <t>95359</t>
   </si>
   <si>
-    <t>88696</t>
-  </si>
-  <si>
-    <t>88697</t>
-  </si>
-  <si>
     <t>93136</t>
   </si>
   <si>
@@ -362,15 +332,6 @@
     <t>89561</t>
   </si>
   <si>
-    <t>88430</t>
-  </si>
-  <si>
-    <t>88431</t>
-  </si>
-  <si>
-    <t>88432</t>
-  </si>
-  <si>
     <t>88628</t>
   </si>
   <si>
@@ -471,6 +432,45 @@
   </si>
   <si>
     <t>36346</t>
+  </si>
+  <si>
+    <t>93169</t>
+  </si>
+  <si>
+    <t>90327</t>
+  </si>
+  <si>
+    <t>90328</t>
+  </si>
+  <si>
+    <t>91060</t>
+  </si>
+  <si>
+    <t>85458</t>
+  </si>
+  <si>
+    <t>78784</t>
+  </si>
+  <si>
+    <t>78785</t>
+  </si>
+  <si>
+    <t>88381</t>
+  </si>
+  <si>
+    <t>88382</t>
+  </si>
+  <si>
+    <t>88324</t>
+  </si>
+  <si>
+    <t>88326</t>
+  </si>
+  <si>
+    <t>88327</t>
+  </si>
+  <si>
+    <t>88298</t>
   </si>
 </sst>
 </file>
@@ -528,43 +528,11 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Combiné"/>
-      <sheetName val="Tableau4"/>
-      <sheetName val="Feuil2"/>
-      <sheetName val="Export"/>
-      <sheetName val="Drug_code-DIN"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
-        <row r="1">
-          <cell r="A1" t="str">
-            <v>drug_code</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B077A580-FBCF-4077-BE05-3DD1481BD4F9}" name="DIN_Verified" displayName="DIN_Verified" ref="A1:A145" totalsRowShown="0">
-  <autoFilter ref="A1:A145" xr:uid="{B077A580-FBCF-4077-BE05-3DD1481BD4F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B077A580-FBCF-4077-BE05-3DD1481BD4F9}" name="DIN_Verified" displayName="DIN_Verified" ref="A1:A146" totalsRowShown="0">
+  <autoFilter ref="A1:A146" xr:uid="{B077A580-FBCF-4077-BE05-3DD1481BD4F9}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{C249E5BC-68BA-49F5-AC38-B02E18C4D224}" name="Drug_code">
-      <calculatedColumnFormula>INDEX([1]Export!$A$1:$B$54486,MATCH([1]!Tableau4_1[[#This Row],[DIN]],[1]Export!$B$1:$B$54486,0),1)</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="1" xr3:uid="{C249E5BC-68BA-49F5-AC38-B02E18C4D224}" name="Drug_code"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -887,7 +855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A84D41-C0A6-412A-A2C4-D8AB6A64AF4A}">
-  <dimension ref="A1:A145"/>
+  <dimension ref="A1:A146"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.5703125" customWidth="1"/>
@@ -1050,572 +1018,577 @@
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>42</v>
+        <v>138</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>54</v>
+        <v>139</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>55</v>
+        <v>140</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>107</v>
+        <v>141</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>108</v>
+        <v>142</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>109</v>
+        <v>143</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" s="1">
-        <v>93440</v>
+      <c r="A117" s="1" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>143</v>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Drugcode_a_verifier.xlsx
+++ b/Data/Drugcode_a_verifier.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mantrapharma.sharepoint.com/sites/602/Documents partages/602-2 Courrier, courriel et messagerie/POWER BI/PowerBI/Affaires Règlementaires/Archives/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FrédérickProvost\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{22615A91-E262-420B-84D6-BBEA28052701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76CFC39A-0FAA-4C2D-B20C-B8C94F12E8B8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A2143B7-ABDD-4DA0-B0E5-7F58715C874B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4E4CF4C5-DE0A-4A25-92E1-A8C1694B9CC3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4E4CF4C5-DE0A-4A25-92E1-A8C1694B9CC3}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,441 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
     <t>Drug_code</t>
-  </si>
-  <si>
-    <t>84031</t>
-  </si>
-  <si>
-    <t>88462</t>
-  </si>
-  <si>
-    <t>88463</t>
-  </si>
-  <si>
-    <t>88464</t>
-  </si>
-  <si>
-    <t>99838</t>
-  </si>
-  <si>
-    <t>103802</t>
-  </si>
-  <si>
-    <t>93699</t>
-  </si>
-  <si>
-    <t>93700</t>
-  </si>
-  <si>
-    <t>93701</t>
-  </si>
-  <si>
-    <t>93702</t>
-  </si>
-  <si>
-    <t>93703</t>
-  </si>
-  <si>
-    <t>92372</t>
-  </si>
-  <si>
-    <t>92373</t>
-  </si>
-  <si>
-    <t>87407</t>
-  </si>
-  <si>
-    <t>87408</t>
-  </si>
-  <si>
-    <t>95045</t>
-  </si>
-  <si>
-    <t>95046</t>
-  </si>
-  <si>
-    <t>92207</t>
-  </si>
-  <si>
-    <t>91148</t>
-  </si>
-  <si>
-    <t>94108</t>
-  </si>
-  <si>
-    <t>94484</t>
-  </si>
-  <si>
-    <t>84080</t>
-  </si>
-  <si>
-    <t>84081</t>
-  </si>
-  <si>
-    <t>84082</t>
-  </si>
-  <si>
-    <t>98239</t>
-  </si>
-  <si>
-    <t>98240</t>
-  </si>
-  <si>
-    <t>94054</t>
-  </si>
-  <si>
-    <t>94055</t>
-  </si>
-  <si>
-    <t>94056</t>
-  </si>
-  <si>
-    <t>94057</t>
-  </si>
-  <si>
-    <t>93170</t>
-  </si>
-  <si>
-    <t>103590</t>
-  </si>
-  <si>
-    <t>97082</t>
-  </si>
-  <si>
-    <t>97083</t>
-  </si>
-  <si>
-    <t>97084</t>
-  </si>
-  <si>
-    <t>90695</t>
-  </si>
-  <si>
-    <t>90696</t>
-  </si>
-  <si>
-    <t>97439</t>
-  </si>
-  <si>
-    <t>97440</t>
-  </si>
-  <si>
-    <t>97441</t>
-  </si>
-  <si>
-    <t>97442</t>
-  </si>
-  <si>
-    <t>95355</t>
-  </si>
-  <si>
-    <t>95356</t>
-  </si>
-  <si>
-    <t>95357</t>
-  </si>
-  <si>
-    <t>95358</t>
-  </si>
-  <si>
-    <t>95359</t>
-  </si>
-  <si>
-    <t>93136</t>
-  </si>
-  <si>
-    <t>93137</t>
-  </si>
-  <si>
-    <t>90658</t>
-  </si>
-  <si>
-    <t>90660</t>
-  </si>
-  <si>
-    <t>103828</t>
-  </si>
-  <si>
-    <t>103829</t>
-  </si>
-  <si>
-    <t>103830</t>
-  </si>
-  <si>
-    <t>90572</t>
-  </si>
-  <si>
-    <t>96300</t>
-  </si>
-  <si>
-    <t>91325</t>
-  </si>
-  <si>
-    <t>87695</t>
-  </si>
-  <si>
-    <t>87696</t>
-  </si>
-  <si>
-    <t>85857</t>
-  </si>
-  <si>
-    <t>103931</t>
-  </si>
-  <si>
-    <t>103932</t>
-  </si>
-  <si>
-    <t>98137</t>
-  </si>
-  <si>
-    <t>96400</t>
-  </si>
-  <si>
-    <t>96401</t>
-  </si>
-  <si>
-    <t>92194</t>
-  </si>
-  <si>
-    <t>92195</t>
-  </si>
-  <si>
-    <t>92754</t>
-  </si>
-  <si>
-    <t>99859</t>
-  </si>
-  <si>
-    <t>89987</t>
-  </si>
-  <si>
-    <t>89988</t>
-  </si>
-  <si>
-    <t>89547</t>
-  </si>
-  <si>
-    <t>89548</t>
-  </si>
-  <si>
-    <t>89549</t>
-  </si>
-  <si>
-    <t>96501</t>
-  </si>
-  <si>
-    <t>96502</t>
-  </si>
-  <si>
-    <t>96503</t>
-  </si>
-  <si>
-    <t>103812</t>
-  </si>
-  <si>
-    <t>103813</t>
-  </si>
-  <si>
-    <t>91539</t>
-  </si>
-  <si>
-    <t>91540</t>
-  </si>
-  <si>
-    <t>91541</t>
-  </si>
-  <si>
-    <t>90072</t>
-  </si>
-  <si>
-    <t>90073</t>
-  </si>
-  <si>
-    <t>90074</t>
-  </si>
-  <si>
-    <t>90075</t>
-  </si>
-  <si>
-    <t>90076</t>
-  </si>
-  <si>
-    <t>90077</t>
-  </si>
-  <si>
-    <t>90078</t>
-  </si>
-  <si>
-    <t>90079</t>
-  </si>
-  <si>
-    <t>86553</t>
-  </si>
-  <si>
-    <t>86554</t>
-  </si>
-  <si>
-    <t>95062</t>
-  </si>
-  <si>
-    <t>95063</t>
-  </si>
-  <si>
-    <t>89558</t>
-  </si>
-  <si>
-    <t>89559</t>
-  </si>
-  <si>
-    <t>89560</t>
-  </si>
-  <si>
-    <t>89561</t>
-  </si>
-  <si>
-    <t>88628</t>
-  </si>
-  <si>
-    <t>88629</t>
-  </si>
-  <si>
-    <t>88630</t>
-  </si>
-  <si>
-    <t>93437</t>
-  </si>
-  <si>
-    <t>93438</t>
-  </si>
-  <si>
-    <t>93439</t>
-  </si>
-  <si>
-    <t>98610</t>
-  </si>
-  <si>
-    <t>95533</t>
-  </si>
-  <si>
-    <t>87120</t>
-  </si>
-  <si>
-    <t>87121</t>
-  </si>
-  <si>
-    <t>103004</t>
-  </si>
-  <si>
-    <t>103006</t>
-  </si>
-  <si>
-    <t>102504</t>
-  </si>
-  <si>
-    <t>102098</t>
-  </si>
-  <si>
-    <t>102099</t>
-  </si>
-  <si>
-    <t>102358</t>
-  </si>
-  <si>
-    <t>103457</t>
-  </si>
-  <si>
-    <t>103458</t>
-  </si>
-  <si>
-    <t>103459</t>
-  </si>
-  <si>
-    <t>87127</t>
-  </si>
-  <si>
-    <t>87128</t>
-  </si>
-  <si>
-    <t>84649</t>
-  </si>
-  <si>
-    <t>89149</t>
-  </si>
-  <si>
-    <t>89150</t>
-  </si>
-  <si>
-    <t>89151</t>
-  </si>
-  <si>
-    <t>90870</t>
-  </si>
-  <si>
-    <t>90871</t>
-  </si>
-  <si>
-    <t>86591</t>
-  </si>
-  <si>
-    <t>86592</t>
-  </si>
-  <si>
-    <t>86593</t>
-  </si>
-  <si>
-    <t>100621</t>
-  </si>
-  <si>
-    <t>100622</t>
-  </si>
-  <si>
-    <t>100623</t>
-  </si>
-  <si>
-    <t>36346</t>
-  </si>
-  <si>
-    <t>93169</t>
-  </si>
-  <si>
-    <t>90327</t>
-  </si>
-  <si>
-    <t>90328</t>
-  </si>
-  <si>
-    <t>91060</t>
-  </si>
-  <si>
-    <t>85458</t>
-  </si>
-  <si>
-    <t>78784</t>
-  </si>
-  <si>
-    <t>78785</t>
-  </si>
-  <si>
-    <t>88381</t>
-  </si>
-  <si>
-    <t>88382</t>
-  </si>
-  <si>
-    <t>88324</t>
-  </si>
-  <si>
-    <t>88326</t>
-  </si>
-  <si>
-    <t>88327</t>
-  </si>
-  <si>
-    <t>88298</t>
   </si>
 </sst>
 </file>
@@ -508,9 +76,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -529,8 +95,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B077A580-FBCF-4077-BE05-3DD1481BD4F9}" name="DIN_Verified" displayName="DIN_Verified" ref="A1:A146" totalsRowShown="0">
-  <autoFilter ref="A1:A146" xr:uid="{B077A580-FBCF-4077-BE05-3DD1481BD4F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B077A580-FBCF-4077-BE05-3DD1481BD4F9}" name="DIN_Verified" displayName="DIN_Verified" ref="A1:A145" totalsRowShown="0">
+  <autoFilter ref="A1:A145" xr:uid="{B077A580-FBCF-4077-BE05-3DD1481BD4F9}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{C249E5BC-68BA-49F5-AC38-B02E18C4D224}" name="Drug_code"/>
   </tableColumns>
@@ -855,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A84D41-C0A6-412A-A2C4-D8AB6A64AF4A}">
-  <dimension ref="A1:A146"/>
+  <dimension ref="A1:A145"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.5703125" customWidth="1"/>
@@ -867,728 +433,723 @@
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
+      <c r="A2" s="1">
+        <v>84031</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
+      <c r="A3" s="1">
+        <v>88462</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
+      <c r="A4" s="1">
+        <v>88463</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
+      <c r="A5" s="1">
+        <v>88464</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>5</v>
+      <c r="A6" s="1">
+        <v>99838</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
+      <c r="A7" s="1">
+        <v>103802</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>7</v>
+      <c r="A8" s="1">
+        <v>93699</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
+      <c r="A9" s="1">
+        <v>93700</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>9</v>
+      <c r="A10" s="1">
+        <v>93701</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>10</v>
+      <c r="A11" s="1">
+        <v>93702</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>11</v>
+      <c r="A12" s="1">
+        <v>93703</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>12</v>
+      <c r="A13" s="1">
+        <v>92372</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>13</v>
+      <c r="A14" s="1">
+        <v>92373</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>14</v>
+      <c r="A15" s="1">
+        <v>87407</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>15</v>
+      <c r="A16" s="1">
+        <v>87408</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>16</v>
+      <c r="A17" s="1">
+        <v>95045</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>17</v>
+      <c r="A18" s="1">
+        <v>95046</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>18</v>
+      <c r="A19" s="1">
+        <v>92207</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>19</v>
+      <c r="A20" s="1">
+        <v>91148</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>20</v>
+      <c r="A21" s="1">
+        <v>94108</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>21</v>
+      <c r="A22" s="1">
+        <v>94484</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>22</v>
+      <c r="A23" s="1">
+        <v>84080</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>23</v>
+      <c r="A24" s="1">
+        <v>84081</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>24</v>
+      <c r="A25" s="1">
+        <v>84082</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>25</v>
+      <c r="A26" s="1">
+        <v>98239</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>26</v>
+      <c r="A27" s="1">
+        <v>98240</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>27</v>
+      <c r="A28" s="1">
+        <v>94054</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>28</v>
+      <c r="A29" s="1">
+        <v>94055</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>29</v>
+      <c r="A30" s="1">
+        <v>94056</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>30</v>
+      <c r="A31" s="1">
+        <v>94057</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>132</v>
+      <c r="A32" s="1">
+        <v>93169</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>31</v>
+      <c r="A33" s="1">
+        <v>93170</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>32</v>
+      <c r="A34" s="1">
+        <v>103590</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>133</v>
+      <c r="A35" s="1">
+        <v>90327</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>134</v>
+      <c r="A36" s="1">
+        <v>90328</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>135</v>
+      <c r="A37" s="1">
+        <v>91060</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>33</v>
+      <c r="A38" s="1">
+        <v>97082</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>34</v>
+      <c r="A39" s="1">
+        <v>97083</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>35</v>
+      <c r="A40" s="1">
+        <v>97084</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>136</v>
+      <c r="A41" s="1">
+        <v>85458</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>137</v>
+      <c r="A42" s="1">
+        <v>78784</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>138</v>
+      <c r="A43" s="1">
+        <v>78785</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>36</v>
+      <c r="A44" s="1">
+        <v>90695</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>37</v>
+      <c r="A45" s="1">
+        <v>90696</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>38</v>
+      <c r="A46" s="1">
+        <v>97439</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>39</v>
+      <c r="A47" s="1">
+        <v>97440</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>40</v>
+      <c r="A48" s="1">
+        <v>97441</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>41</v>
+      <c r="A49" s="1">
+        <v>97442</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>42</v>
+      <c r="A50" s="1">
+        <v>95355</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>43</v>
+      <c r="A51" s="1">
+        <v>95356</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>44</v>
+      <c r="A52" s="1">
+        <v>95357</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>45</v>
+      <c r="A53" s="1">
+        <v>95358</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>46</v>
+      <c r="A54" s="1">
+        <v>95359</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>139</v>
+      <c r="A55" s="1">
+        <v>88381</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>140</v>
+      <c r="A56" s="1">
+        <v>88382</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>47</v>
+      <c r="A57" s="1">
+        <v>93136</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>48</v>
+      <c r="A58" s="1">
+        <v>93137</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>49</v>
+      <c r="A59" s="1">
+        <v>90658</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>50</v>
+      <c r="A60" s="1">
+        <v>90660</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>51</v>
+      <c r="A61" s="1">
+        <v>103828</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>52</v>
+      <c r="A62" s="1">
+        <v>103829</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>53</v>
+      <c r="A63" s="1">
+        <v>103830</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>54</v>
+      <c r="A64" s="1">
+        <v>90572</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>55</v>
+      <c r="A65" s="1">
+        <v>96300</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>56</v>
+      <c r="A66" s="1">
+        <v>91325</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>57</v>
+      <c r="A67" s="1">
+        <v>87695</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>58</v>
+      <c r="A68" s="1">
+        <v>87696</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>59</v>
+      <c r="A69" s="1">
+        <v>85857</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>60</v>
+      <c r="A70" s="1">
+        <v>103931</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>61</v>
+      <c r="A71" s="1">
+        <v>103932</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>62</v>
+      <c r="A72" s="1">
+        <v>98137</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>63</v>
+      <c r="A73" s="1">
+        <v>96400</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>64</v>
+      <c r="A74" s="1">
+        <v>96401</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>65</v>
+      <c r="A75" s="1">
+        <v>92194</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>66</v>
+      <c r="A76" s="1">
+        <v>92195</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>67</v>
+      <c r="A77" s="1">
+        <v>92754</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>68</v>
+      <c r="A78" s="1">
+        <v>99859</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>69</v>
+      <c r="A79" s="1">
+        <v>89987</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>70</v>
+      <c r="A80" s="1">
+        <v>89988</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>71</v>
+      <c r="A81" s="1">
+        <v>89547</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>72</v>
+      <c r="A82" s="1">
+        <v>89548</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>73</v>
+      <c r="A83" s="1">
+        <v>89549</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>74</v>
+      <c r="A84" s="1">
+        <v>96501</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>75</v>
+      <c r="A85" s="1">
+        <v>96502</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>76</v>
+      <c r="A86" s="1">
+        <v>96503</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>77</v>
+      <c r="A87" s="1">
+        <v>103812</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>78</v>
+      <c r="A88" s="1">
+        <v>103813</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>79</v>
+      <c r="A89" s="1">
+        <v>91539</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>80</v>
+      <c r="A90" s="1">
+        <v>91540</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>81</v>
+      <c r="A91" s="1">
+        <v>91541</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>82</v>
+      <c r="A92" s="1">
+        <v>90072</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>83</v>
+      <c r="A93" s="1">
+        <v>90073</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>84</v>
+      <c r="A94" s="1">
+        <v>90074</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>85</v>
+      <c r="A95" s="1">
+        <v>90075</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>86</v>
+      <c r="A96" s="1">
+        <v>90076</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>87</v>
+      <c r="A97" s="1">
+        <v>90077</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>88</v>
+      <c r="A98" s="1">
+        <v>90078</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>89</v>
+      <c r="A99" s="1">
+        <v>90079</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>90</v>
+      <c r="A100" s="1">
+        <v>86553</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>91</v>
+      <c r="A101" s="1">
+        <v>86554</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>92</v>
+      <c r="A102" s="1">
+        <v>95062</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>93</v>
+      <c r="A103" s="1">
+        <v>95063</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>94</v>
+      <c r="A104" s="1">
+        <v>89558</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>95</v>
+      <c r="A105" s="1">
+        <v>89559</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>96</v>
+      <c r="A106" s="1">
+        <v>89560</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>97</v>
+      <c r="A107" s="1">
+        <v>89561</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>141</v>
+      <c r="A108" s="1">
+        <v>88324</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>142</v>
+      <c r="A109" s="1">
+        <v>88326</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>143</v>
+      <c r="A110" s="1">
+        <v>88327</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>98</v>
+      <c r="A111" s="1">
+        <v>88628</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>99</v>
+      <c r="A112" s="1">
+        <v>88629</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>100</v>
+      <c r="A113" s="1">
+        <v>88630</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>101</v>
+      <c r="A114" s="1">
+        <v>93437</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>102</v>
+      <c r="A115" s="1">
+        <v>93438</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>103</v>
+      <c r="A116" s="1">
+        <v>93439</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="e">
-        <v>#N/A</v>
+      <c r="A117" s="1">
+        <v>98610</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>104</v>
+      <c r="A118" s="1">
+        <v>95533</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>105</v>
+      <c r="A119" s="1">
+        <v>87120</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>106</v>
+      <c r="A120" s="1">
+        <v>87121</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>107</v>
+      <c r="A121" s="1">
+        <v>88298</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>144</v>
+      <c r="A122" s="1">
+        <v>103004</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>108</v>
+      <c r="A123" s="1">
+        <v>103006</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>109</v>
+      <c r="A124" s="1">
+        <v>102504</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>110</v>
+      <c r="A125" s="1">
+        <v>102098</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>111</v>
+      <c r="A126" s="1">
+        <v>102099</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>112</v>
+      <c r="A127" s="1">
+        <v>102358</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>113</v>
+      <c r="A128" s="1">
+        <v>103457</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>114</v>
+      <c r="A129" s="1">
+        <v>103458</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>115</v>
+      <c r="A130" s="1">
+        <v>103459</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>116</v>
+      <c r="A131" s="1">
+        <v>87127</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>117</v>
+      <c r="A132" s="1">
+        <v>87128</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>118</v>
+      <c r="A133" s="1">
+        <v>84649</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>119</v>
+      <c r="A134" s="1">
+        <v>89149</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>120</v>
+      <c r="A135" s="1">
+        <v>89150</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>121</v>
+      <c r="A136" s="1">
+        <v>89151</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>122</v>
+      <c r="A137" s="1">
+        <v>90870</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>123</v>
+      <c r="A138" s="1">
+        <v>90871</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>124</v>
+      <c r="A139" s="1">
+        <v>86591</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>125</v>
+      <c r="A140" s="1">
+        <v>86592</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>126</v>
+      <c r="A141" s="1">
+        <v>86593</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>127</v>
+      <c r="A142" s="1">
+        <v>100621</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>128</v>
+      <c r="A143" s="1">
+        <v>100622</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>129</v>
+      <c r="A144" s="1">
+        <v>100623</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>131</v>
+      <c r="A145" s="1">
+        <v>36346</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Drugcode_a_verifier.xlsx
+++ b/Data/Drugcode_a_verifier.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FrédérickProvost\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frede\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A2143B7-ABDD-4DA0-B0E5-7F58715C874B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C322C081-D3D2-4FDA-9A9D-86B050F99AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4E4CF4C5-DE0A-4A25-92E1-A8C1694B9CC3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4E4CF4C5-DE0A-4A25-92E1-A8C1694B9CC3}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -94,8 +94,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B077A580-FBCF-4077-BE05-3DD1481BD4F9}" name="DIN_Verified" displayName="DIN_Verified" ref="A1:A145" totalsRowShown="0">
-  <autoFilter ref="A1:A145" xr:uid="{B077A580-FBCF-4077-BE05-3DD1481BD4F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B077A580-FBCF-4077-BE05-3DD1481BD4F9}" name="DIN_Verified" displayName="DIN_Verified" ref="A1:A147" totalsRowShown="0">
+  <autoFilter ref="A1:A147" xr:uid="{B077A580-FBCF-4077-BE05-3DD1481BD4F9}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{C249E5BC-68BA-49F5-AC38-B02E18C4D224}" name="Drug_code"/>
   </tableColumns>
@@ -420,7 +420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A84D41-C0A6-412A-A2C4-D8AB6A64AF4A}">
-  <dimension ref="A1:A145"/>
+  <dimension ref="A1:A147"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.5703125" customWidth="1"/>
@@ -1149,6 +1149,16 @@
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>36346</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>15209</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>62268</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Drugcode_a_verifier.xlsx
+++ b/Data/Drugcode_a_verifier.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frede\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C322C081-D3D2-4FDA-9A9D-86B050F99AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3292A9ED-FB66-497D-BCC7-C78730815AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4E4CF4C5-DE0A-4A25-92E1-A8C1694B9CC3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4E4CF4C5-DE0A-4A25-92E1-A8C1694B9CC3}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -74,8 +74,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -94,8 +95,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B077A580-FBCF-4077-BE05-3DD1481BD4F9}" name="DIN_Verified" displayName="DIN_Verified" ref="A1:A147" totalsRowShown="0">
-  <autoFilter ref="A1:A147" xr:uid="{B077A580-FBCF-4077-BE05-3DD1481BD4F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B077A580-FBCF-4077-BE05-3DD1481BD4F9}" name="DIN_Verified" displayName="DIN_Verified" ref="A1:A169" totalsRowShown="0">
+  <autoFilter ref="A1:A169" xr:uid="{B077A580-FBCF-4077-BE05-3DD1481BD4F9}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{C249E5BC-68BA-49F5-AC38-B02E18C4D224}" name="Drug_code"/>
   </tableColumns>
@@ -420,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A84D41-C0A6-412A-A2C4-D8AB6A64AF4A}">
-  <dimension ref="A1:A147"/>
+  <dimension ref="A1:A169"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.5703125" customWidth="1"/>
@@ -1159,6 +1160,116 @@
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>62268</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" s="1">
+        <v>43182</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" s="1">
+        <v>90088</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" s="1">
+        <v>94181</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" s="1">
+        <v>85352</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" s="1">
+        <v>15208</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" s="1">
+        <v>62269</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" s="1">
+        <v>15209</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" s="1">
+        <v>62268</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" s="1">
+        <v>91977</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" s="1">
+        <v>91978</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" s="1">
+        <v>106406</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" s="1">
+        <v>90029</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160" s="1">
+        <v>15231</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" s="1">
+        <v>86025</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" s="1">
+        <v>97146</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" s="1">
+        <v>80247</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" s="1">
+        <v>86439</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" s="1">
+        <v>86440</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" s="1">
+        <v>79274</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" s="1">
+        <v>79275</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" s="1">
+        <v>92871</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" s="1">
+        <v>92872</v>
       </c>
     </row>
   </sheetData>
